--- a/results/prediction_results.xlsx
+++ b/results/prediction_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NCHU\大三_解釋型AI與資料治理\xai_learning_lab\XAI-HCI\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41FEF6D-69A3-4CF3-B01B-44344E5AD908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C91134C-F66C-4B20-A57A-157144F8C2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="3750" windowWidth="9780" windowHeight="7620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="208">
   <si>
     <t>檔名</t>
   </si>
@@ -49,21 +49,12 @@
     <t>X</t>
   </si>
   <si>
-    <t>Huang_Boredom_04_orig.jpg</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
-    <t>Huang_Boredom_06_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Boredom_18_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Boredom_23_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Boredom_24_orig.jpg</t>
   </si>
   <si>
@@ -73,21 +64,12 @@
     <t>Huang_Boredom_d02_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Boredom_01_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Boredom_03_orig.jpg</t>
   </si>
   <si>
     <t>Yo_Boredom_04_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Boredom_05_orig.jpg</t>
-  </si>
-  <si>
-    <t>Yo_Boredom_06_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Boredom_07_orig.jpg</t>
   </si>
   <si>
@@ -115,9 +97,6 @@
     <t>Yo_Boredom_25_orig.jpg</t>
   </si>
   <si>
-    <t>yu_Boredom_04_orig.jpg</t>
-  </si>
-  <si>
     <t>yu_Boredom_19_orig.jpg</t>
   </si>
   <si>
@@ -127,39 +106,21 @@
     <t>投入</t>
   </si>
   <si>
-    <t>yu_Boredom_24_orig.jpg</t>
-  </si>
-  <si>
-    <t>yu_Boredom_25_orig.jpg</t>
-  </si>
-  <si>
     <t>Yu_Boredom_d05_orig.jpg</t>
   </si>
   <si>
     <t>Huang_Confusion_04_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Confusion_07_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Confusion_d03_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Confusion_d05_orig.jpg</t>
-  </si>
-  <si>
-    <t>Yo_Confusion_01_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Confusion_02_orig.jpg</t>
   </si>
   <si>
     <t>喜悅</t>
   </si>
   <si>
-    <t>Yo_Confusion_03_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Confusion_04_orig.jpg</t>
   </si>
   <si>
@@ -169,9 +130,6 @@
     <t>Yo_Confusion_06_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Confusion_08_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Confusion_09_orig.jpg</t>
   </si>
   <si>
@@ -184,9 +142,6 @@
     <t>Yo_Confusion_19_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Confusion_21_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Confusion_22_orig.jpg</t>
   </si>
   <si>
@@ -202,15 +157,9 @@
     <t>yu_Confusion_04_orig.jpg</t>
   </si>
   <si>
-    <t>yu_Confusion_19_orig.jpg</t>
-  </si>
-  <si>
     <t>Yu_Confusion_d02_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Delight_01_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Delight_04_orig.jpg</t>
   </si>
   <si>
@@ -223,15 +172,6 @@
     <t>Huang_Delight_08_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Delight_10_orig.jpg</t>
-  </si>
-  <si>
-    <t>Huang_Delight_19_orig.jpg</t>
-  </si>
-  <si>
-    <t>Yo_Delight_01_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Delight_02_orig.jpg</t>
   </si>
   <si>
@@ -265,9 +205,6 @@
     <t>Yo_Delight_23_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Delight_25_orig.jpg</t>
-  </si>
-  <si>
     <t>yu_Delight_01_orig.jpg</t>
   </si>
   <si>
@@ -280,9 +217,6 @@
     <t>yu_Delight_10_orig.jpg</t>
   </si>
   <si>
-    <t>yu_Delight_19_orig.jpg</t>
-  </si>
-  <si>
     <t>yu_Delight_21_orig.jpg</t>
   </si>
   <si>
@@ -295,18 +229,12 @@
     <t>Yu_Delight_d04_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Engagement_02_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Engagement_05_orig.jpg</t>
   </si>
   <si>
     <t>Huang_Engagement_06_orig.jpg</t>
   </si>
   <si>
-    <t>Huang_Engagement_09_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Engagement_18_orig.jpg</t>
   </si>
   <si>
@@ -349,9 +277,6 @@
     <t>Yo_Engagement_20_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Engagement_21_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Engagement_22_orig.jpg</t>
   </si>
   <si>
@@ -412,15 +337,9 @@
     <t>Yo_Frustration_03_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Frustration_06_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Frustration_07_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Frustration_08_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Frustration_10_orig.jpg</t>
   </si>
   <si>
@@ -430,9 +349,6 @@
     <t>Yo_Frustration_19_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Frustration_20_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Frustration_21_orig.jpg</t>
   </si>
   <si>
@@ -469,9 +385,6 @@
     <t>yu_Frustration_25_orig.jpg</t>
   </si>
   <si>
-    <t>Yu_Frustration_d02_orig.jpg</t>
-  </si>
-  <si>
     <t>Huang_Surprise_01_orig.jpg</t>
   </si>
   <si>
@@ -514,9 +427,6 @@
     <t>Yo_Surprise_04_orig.jpg</t>
   </si>
   <si>
-    <t>Yo_Surprise_10_orig.jpg</t>
-  </si>
-  <si>
     <t>Yo_Surprise_19_orig.jpg</t>
   </si>
   <si>
@@ -532,9 +442,6 @@
     <t>Yo_Surprise_25_orig.jpg</t>
   </si>
   <si>
-    <t>yu_Surprise_02_orig.jpg</t>
-  </si>
-  <si>
     <t>yu_Surprise_05_orig.jpg</t>
   </si>
   <si>
@@ -554,9 +461,6 @@
   </si>
   <si>
     <t>yu_Surprise_24_orig.jpg</t>
-  </si>
-  <si>
-    <t>yu_Surprise_d02_orig.jpg</t>
   </si>
   <si>
     <t>yu_Surprise_d04_orig.jpg</t>
@@ -652,6 +556,134 @@
   </si>
   <si>
     <t>困惑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Boredom_04_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Boredom_06_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Boredom_04_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Confusion_07_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Confusion_08_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Delight_10_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Surprise_10_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Surprise_02_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yu_Frustration_d02_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Delight_01_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Delight_25_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Engagement_09_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Engagement_21_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Confusion_21_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Boredom_23_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Boredom_01_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Boredom_24_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Confusion_03_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Frustration_06_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Frustration_20_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Frustration_08_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Confusion_d05_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Boredom_06_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Boredom_05_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Boredom_25_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Confusion_01_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Confusion_19_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Delight_19_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yo_Delight_01_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Delight_19_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huang_Engagement_02_orig.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>yu_Surprise_d02_orig.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -738,7 +770,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1066,22 +1098,22 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="O1" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="P1" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="Q1" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="R1" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="S1" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1101,27 +1133,27 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="O2" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="P2" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="Q2" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="R2" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="S2" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1133,30 +1165,30 @@
         <v>0.51870000000000005</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="O3" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="Q3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="R3" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="S3" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -1168,30 +1200,30 @@
         <v>0.76949999999999996</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="O4" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="Q4" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="R4" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="S4" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -1203,36 +1235,36 @@
         <v>0.44969999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="O5" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="Q5" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="R5" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="S5" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="D6">
         <v>0.45579999999999998</v>
@@ -1241,12 +1273,12 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -1258,15 +1290,15 @@
         <v>0.31709999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -1278,15 +1310,15 @@
         <v>0.51800000000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
@@ -1301,12 +1333,12 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -1321,12 +1353,12 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -1338,15 +1370,15 @@
         <v>0.72589999999999999</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -1358,15 +1390,15 @@
         <v>0.59770000000000001</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -1378,15 +1410,15 @@
         <v>0.90549999999999997</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
@@ -1398,15 +1430,15 @@
         <v>0.82099999999999995</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
@@ -1418,15 +1450,15 @@
         <v>0.45750000000000002</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
@@ -1438,15 +1470,15 @@
         <v>0.58099999999999996</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -1458,15 +1490,15 @@
         <v>0.4607</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
@@ -1478,15 +1510,15 @@
         <v>0.47749999999999998</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
         <v>6</v>
@@ -1503,13 +1535,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D20">
         <v>0.46889999999999998</v>
@@ -1518,18 +1550,18 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>0.40889999999999999</v>
@@ -1538,12 +1570,12 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -1555,15 +1587,15 @@
         <v>0.74719999999999998</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
@@ -1575,15 +1607,15 @@
         <v>0.78129999999999999</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
@@ -1598,18 +1630,18 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D25">
         <v>0.6865</v>
@@ -1618,18 +1650,18 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D26">
         <v>0.6351</v>
@@ -1638,12 +1670,12 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="B27" t="s">
         <v>6</v>
@@ -1655,15 +1687,15 @@
         <v>0.77829999999999999</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
         <v>6</v>
@@ -1675,15 +1707,15 @@
         <v>0.60450000000000004</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -1695,15 +1727,15 @@
         <v>0.55110000000000003</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -1715,15 +1747,15 @@
         <v>0.75890000000000002</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -1735,21 +1767,21 @@
         <v>0.56769999999999998</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D32">
         <v>0.34889999999999999</v>
@@ -1758,12 +1790,12 @@
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -1775,21 +1807,21 @@
         <v>0.77529999999999999</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D34">
         <v>0.63080000000000003</v>
@@ -1798,12 +1830,12 @@
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -1818,12 +1850,12 @@
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -1835,15 +1867,15 @@
         <v>0.78900000000000003</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -1858,12 +1890,12 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
@@ -1875,12 +1907,12 @@
         <v>0.42280000000000001</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
         <v>7</v>
@@ -1892,15 +1924,15 @@
         <v>0.65890000000000004</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
@@ -1912,12 +1944,12 @@
         <v>0.61950000000000005</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -1929,12 +1961,12 @@
         <v>0.874</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -1946,15 +1978,15 @@
         <v>0.69699999999999995</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -1966,21 +1998,21 @@
         <v>0.51259999999999994</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D44">
         <v>0.61</v>
@@ -1989,18 +2021,18 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D45">
         <v>0.83430000000000004</v>
@@ -2009,18 +2041,18 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D46">
         <v>0.70250000000000001</v>
@@ -2029,18 +2061,18 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D47">
         <v>0.37090000000000001</v>
@@ -2049,12 +2081,12 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
         <v>7</v>
@@ -2066,21 +2098,21 @@
         <v>0.62729999999999997</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
         <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D49">
         <v>0.50070000000000003</v>
@@ -2089,12 +2121,12 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
@@ -2106,15 +2138,15 @@
         <v>0.85960000000000003</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
         <v>7</v>
@@ -2126,1156 +2158,1159 @@
         <v>0.63090000000000002</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D52">
         <v>0.99739999999999995</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D53">
         <v>0.99819999999999998</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D54">
         <v>0.68259999999999998</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D55">
         <v>0.95930000000000004</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F55" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D56">
         <v>0.99509999999999998</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D57">
         <v>0.83209999999999995</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D58">
         <v>0.8881</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D59">
         <v>0.98909999999999998</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D60">
         <v>0.99690000000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D61">
         <v>0.89829999999999999</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D62">
         <v>0.99880000000000002</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D63">
         <v>0.94610000000000005</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D64">
         <v>0.97960000000000003</v>
       </c>
       <c r="E64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D65">
         <v>0.99960000000000004</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D66">
         <v>0.99299999999999999</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D67">
         <v>0.99729999999999996</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D68">
         <v>0.65169999999999995</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D69">
         <v>0.97260000000000002</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D70">
         <v>0.99609999999999999</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D71">
         <v>0.99890000000000001</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D72">
         <v>0.99570000000000003</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D73">
         <v>0.96530000000000005</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D74">
         <v>0.92700000000000005</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D75">
         <v>0.99739999999999995</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>205</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D76">
         <v>0.99980000000000002</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D77">
         <v>0.98089999999999999</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D78">
         <v>0.94550000000000001</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D79">
         <v>0.96860000000000002</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D80">
         <v>0.96460000000000001</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D81">
         <v>0.7429</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D82">
         <v>0.97809999999999997</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D83">
         <v>0.93149999999999999</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D84">
         <v>0.94489999999999996</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D85">
         <v>0.9829</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C86" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D86">
         <v>0.98170000000000002</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D87">
         <v>0.95550000000000002</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D88">
         <v>0.95289999999999997</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D89">
         <v>0.91390000000000005</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C90" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>0.98209999999999997</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D91">
         <v>0.70479999999999998</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D92">
         <v>0.7</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D93">
         <v>0.97399999999999998</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D94">
         <v>0.97899999999999998</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D95">
         <v>0.75090000000000001</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C96" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D96">
         <v>0.89219999999999999</v>
       </c>
       <c r="E96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D97">
         <v>0.7298</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C98" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D98">
         <v>0.75239999999999996</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>188</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D99">
         <v>0.84109999999999996</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C100" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>0.83760000000000001</v>
       </c>
       <c r="E100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D101">
         <v>0.93540000000000001</v>
       </c>
       <c r="E101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F101" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D102">
         <v>0.94750000000000001</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D103">
         <v>0.90590000000000004</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F103" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D104">
         <v>0.96950000000000003</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F104" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C105" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D105">
         <v>0.61480000000000001</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C106" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D106">
         <v>0.41149999999999998</v>
       </c>
       <c r="E106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F106" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C107" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D107">
         <v>0.76359999999999995</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D108">
         <v>0.39650000000000002</v>
       </c>
       <c r="E108" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F108" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C109" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D109">
         <v>0.72060000000000002</v>
       </c>
       <c r="E109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F109" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D110">
         <v>0.52890000000000004</v>
       </c>
       <c r="E110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C111" t="s">
         <v>7</v>
@@ -3289,170 +3324,170 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D112">
         <v>0.4481</v>
       </c>
       <c r="E112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F112" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D113">
         <v>0.84499999999999997</v>
       </c>
       <c r="E113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F113" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D114">
         <v>0.55210000000000004</v>
       </c>
       <c r="E114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D115">
         <v>0.66769999999999996</v>
       </c>
       <c r="E115" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F115" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D116">
         <v>0.76300000000000001</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F116" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C117" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D117">
         <v>0.38879999999999998</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F117" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D118">
         <v>0.74809999999999999</v>
       </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F118" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D119">
         <v>0.48530000000000001</v>
       </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C120" t="s">
         <v>7</v>
@@ -3464,38 +3499,38 @@
         <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D121">
         <v>0.72130000000000005</v>
       </c>
       <c r="E121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F121" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D122">
         <v>0.63549999999999995</v>
@@ -3504,75 +3539,75 @@
         <v>8</v>
       </c>
       <c r="F122" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D123">
         <v>0.54549999999999998</v>
       </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F123" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D124">
         <v>0.6714</v>
       </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F124" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D125">
         <v>0.59109999999999996</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F125" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C126" t="s">
         <v>7</v>
@@ -3584,166 +3619,166 @@
         <v>8</v>
       </c>
       <c r="F126" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D127">
         <v>0.93200000000000005</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D128">
         <v>0.70620000000000005</v>
       </c>
       <c r="E128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F128" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D129">
         <v>0.73070000000000002</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F129" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D130">
         <v>0.82920000000000005</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="B131" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D131">
         <v>0.98009999999999997</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D132">
         <v>0.79279999999999995</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="B133" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D133">
         <v>0.79100000000000004</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="B134" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C134" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D134">
         <v>0.64339999999999997</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F134" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D135">
         <v>0.34770000000000001</v>
@@ -3752,269 +3787,269 @@
         <v>8</v>
       </c>
       <c r="F135" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="B136" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D136">
         <v>0.85389999999999999</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F136" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="B137" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D137">
         <v>0.9456</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F137" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D138">
         <v>0.52280000000000004</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F138" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C139" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D139">
         <v>0.99990000000000001</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C140" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D140">
         <v>0.99960000000000004</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C141" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D141">
         <v>0.85760000000000003</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B142" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C142" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D142">
         <v>0.96779999999999999</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F142" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="B143" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C143" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D143">
         <v>0.99970000000000003</v>
       </c>
       <c r="E143" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="B144" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C144" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D144">
         <v>0.99509999999999998</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F144" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="B145" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C145" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D145">
         <v>0.99850000000000005</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F145" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C146" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D146">
         <v>0.99509999999999998</v>
       </c>
       <c r="E146" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C147" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D147">
         <v>0.99990000000000001</v>
       </c>
       <c r="E147" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C148" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D148">
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F148" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D149">
         <v>0.73119999999999996</v>
@@ -4023,52 +4058,52 @@
         <v>8</v>
       </c>
       <c r="F149" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C150" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D150">
         <v>0.9919</v>
       </c>
       <c r="E150" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C151" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D151">
         <v>0.99509999999999998</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F151" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="B152" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C152" t="s">
         <v>6</v>
@@ -4080,324 +4115,324 @@
         <v>8</v>
       </c>
       <c r="F152" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B153" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C153" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F153" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="B154" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C154" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D154">
         <v>0.95179999999999998</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F154" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B155" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C155" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F155" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="B156" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C156" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D156">
         <v>0.98750000000000004</v>
       </c>
       <c r="E156" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="B157" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C157" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D157">
         <v>0.91120000000000001</v>
       </c>
       <c r="E157" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F157" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="B158" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C158" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F158" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B159" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C159" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D159">
         <v>0.95740000000000003</v>
       </c>
       <c r="E159" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F159" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="B160" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C160" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D160">
         <v>0.99990000000000001</v>
       </c>
       <c r="E160" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F160" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="B161" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C161" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D161">
         <v>0.99990000000000001</v>
       </c>
       <c r="E161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F161" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="B162" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C162" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D162">
         <v>0.76090000000000002</v>
       </c>
       <c r="E162" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F162" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="B163" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C163" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D163">
         <v>0.99639999999999995</v>
       </c>
       <c r="E163" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F163" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B164" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C164" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D164">
         <v>0.99960000000000004</v>
       </c>
       <c r="E164" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F164" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="B165" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C165" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D165">
         <v>0.98470000000000002</v>
       </c>
       <c r="E165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F165" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C166" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D166">
         <v>0.51900000000000002</v>
       </c>
       <c r="E166" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="B167" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C167" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D167">
         <v>0.99829999999999997</v>
       </c>
       <c r="E167" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F167" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="B168" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C168" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D168">
         <v>0.995</v>
       </c>
       <c r="E168" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F168" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
